--- a/src/test/resources/data.xlsx
+++ b/src/test/resources/data.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{F8F63C94-48F4-4427-8493-404C81954B51}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{6204EB2F-6E04-4A87-A97B-58C679C628B8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16440" windowHeight="3300" activeTab="1" xr2:uid="{8666860D-7FE1-4D9B-88DC-AC3EA951CFC0}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16155" windowHeight="3420" activeTab="1" xr2:uid="{8666860D-7FE1-4D9B-88DC-AC3EA951CFC0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
